--- a/excels/2급_전산회계책_분개.xlsx
+++ b/excels/2급_전산회계책_분개.xlsx
@@ -1,21 +1,20 @@
 
-<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
-  <sheets>
-    <sheet name="문제" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="정답및해설" sheetId="2" state="visible" r:id="rId2"/>
-  </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
-</workbook>
+<file path=docProps\app.xml><?xml version="1.0" encoding="utf-8"?>
+<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties">
+  <Application>Microsoft Excel Compatible / Openpyxl 3.1.5</Application>
+  <AppVersion>3.1</AppVersion>
+</Properties>
 </file>
 
-<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=docProps\core.xml><?xml version="1.0" encoding="utf-8"?>
+<cp:coreProperties xmlns:cp="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
+  <dc:creator>openpyxl</dc:creator>
+  <dcterms:created xsi:type="dcterms:W3CDTF">2026-08-22T15:09:30Z</dcterms:created>
+  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-08-22T15:09:30Z</dcterms:modified>
+</cp:coreProperties>
+</file>
+
+<file path=xl\styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
   <fonts count="1">
@@ -125,7 +124,7 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\theme\theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
@@ -408,7 +407,23 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
+  <sheets>
+    <sheet name="문제" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="정답및해설" sheetId="2" state="visible" r:id="rId2"/>
+  </sheets>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+</workbook>
+</file>
+
+<file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9463,7 +9478,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9510,7 +9525,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>임차료</t>
+          <t>임차료(판)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -9660,7 +9675,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>수수료비용</t>
+          <t>수수료비용(판)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -9690,7 +9705,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>복리후생비</t>
+          <t>복리후생비(판)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -9720,7 +9735,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>통신비</t>
+          <t>통신비(판)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -9810,7 +9825,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>광고선전비</t>
+          <t>광고선전비(판)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -10140,7 +10155,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>복리후생비</t>
+          <t>복리후생비(판)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -10170,7 +10185,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -10200,7 +10215,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>세금과공과</t>
+          <t>세금과공과(판)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -10260,7 +10275,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>수선비</t>
+          <t>수선비(판)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -10380,7 +10395,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>복리후생비</t>
+          <t>복리후생비(판)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -10590,7 +10605,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -10620,7 +10635,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>차량유지비</t>
+          <t>차량유지비(판)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -10800,7 +10815,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>수선비</t>
+          <t>수선비(판)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -10830,7 +10845,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>수수료비용</t>
+          <t>수수료비용(판)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -10950,7 +10965,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>운반비</t>
+          <t>운반비(판)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -10980,7 +10995,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>여비교통비</t>
+          <t>여비교통비(판)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -11130,7 +11145,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>복리후생비</t>
+          <t>복리후생비(판)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -11220,7 +11235,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -11370,7 +11385,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>수선비</t>
+          <t>수선비(판)</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -11670,7 +11685,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>임차료</t>
+          <t>임차료(판)</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -11850,7 +11865,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>세금과공과</t>
+          <t>세금과공과(판)</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -11940,7 +11955,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>수도광열비</t>
+          <t>수도광열비(판)</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -12060,7 +12075,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -12420,7 +12435,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>세금과공과</t>
+          <t>세금과공과(판)</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -12480,7 +12495,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>복리후생비</t>
+          <t>복리후생비(판)</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -12510,7 +12525,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>광고선전비</t>
+          <t>광고선전비(판)</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -12660,7 +12675,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>광고선전비</t>
+          <t>광고선전비(판)</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -12720,7 +12735,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>수선비</t>
+          <t>수선비(판)</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">

--- a/excels/2급_전산회계책_분개.xlsx
+++ b/excels/2급_전산회계책_분개.xlsx
@@ -1,20 +1,21 @@
 
-<file path=docProps\app.xml><?xml version="1.0" encoding="utf-8"?>
-<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties">
-  <Application>Microsoft Excel Compatible / Openpyxl 3.1.5</Application>
-  <AppVersion>3.1</AppVersion>
-</Properties>
+<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
+  <sheets>
+    <sheet name="문제" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="정답및해설" sheetId="2" state="visible" r:id="rId2"/>
+  </sheets>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+</workbook>
 </file>
 
-<file path=docProps\core.xml><?xml version="1.0" encoding="utf-8"?>
-<cp:coreProperties xmlns:cp="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
-  <dc:creator>openpyxl</dc:creator>
-  <dcterms:created xsi:type="dcterms:W3CDTF">2026-08-22T15:09:30Z</dcterms:created>
-  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-08-22T15:09:30Z</dcterms:modified>
-</cp:coreProperties>
-</file>
-
-<file path=xl\styles.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
   <fonts count="1">
@@ -124,7 +125,7 @@
 </styleSheet>
 </file>
 
-<file path=xl\theme\theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
@@ -407,23 +408,7 @@
 </a:theme>
 </file>
 
-<file path=xl\workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
-  <sheets>
-    <sheet name="문제" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="정답및해설" sheetId="2" state="visible" r:id="rId2"/>
-  </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
-</workbook>
-</file>
-
-<file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9478,7 +9463,7 @@
 </worksheet>
 </file>
 
-<file path=xl\worksheets\sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9528,20 +9513,16 @@
           <t>임차료(판)</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>900000</t>
-        </is>
+      <c r="C2" t="n">
+        <v>900000</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>보통예금</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>900000</t>
-        </is>
+      <c r="E2" t="n">
+        <v>900000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -9558,20 +9539,16 @@
           <t>받을어음</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>15000000</t>
-        </is>
+      <c r="C3" t="n">
+        <v>15000000</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>15000000</t>
-        </is>
+      <c r="E3" t="n">
+        <v>15000000</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -9588,20 +9565,16 @@
           <t>기업업무추진비</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>200000</t>
-        </is>
+      <c r="C4" t="n">
+        <v>200000</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>보통예금</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>200000</t>
-        </is>
+      <c r="E4" t="n">
+        <v>200000</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -9618,20 +9591,16 @@
           <t>감가상각누계액</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>50000000</t>
-        </is>
+      <c r="C5" t="n">
+        <v>50000000</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>차량운반구</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>50000000</t>
-        </is>
+      <c r="E5" t="n">
+        <v>50000000</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -9648,20 +9617,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>52500000</t>
-        </is>
+      <c r="C6" t="n">
+        <v>52500000</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>정기예금</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>52500000</t>
-        </is>
+      <c r="E6" t="n">
+        <v>52500000</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -9678,20 +9643,16 @@
           <t>수수료비용(판)</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>5000000</t>
-        </is>
+      <c r="C7" t="n">
+        <v>5000000</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>보통예금</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>5000000</t>
-        </is>
+      <c r="E7" t="n">
+        <v>5000000</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -9708,20 +9669,16 @@
           <t>복리후생비(판)</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>300000</t>
-        </is>
+      <c r="C8" t="n">
+        <v>300000</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
           <t>미지급금</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>300000</t>
-        </is>
+      <c r="E8" t="n">
+        <v>300000</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -9738,20 +9695,16 @@
           <t>통신비(판)</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>100000</t>
-        </is>
+      <c r="C9" t="n">
+        <v>100000</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
           <t>현금</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>100000</t>
-        </is>
+      <c r="E9" t="n">
+        <v>100000</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -9768,20 +9721,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1000000</t>
-        </is>
+      <c r="C10" t="n">
+        <v>1000000</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>1000000</t>
-        </is>
+      <c r="E10" t="n">
+        <v>1000000</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -9798,20 +9747,16 @@
           <t>임차보증금</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>13000000</t>
-        </is>
+      <c r="C11" t="n">
+        <v>13000000</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
           <t>보통예금</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>13000000</t>
-        </is>
+      <c r="E11" t="n">
+        <v>13000000</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -9828,20 +9773,16 @@
           <t>광고선전비(판)</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>3000000</t>
-        </is>
+      <c r="C12" t="n">
+        <v>3000000</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
           <t>미지급금또는미지급비용</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>3000000</t>
-        </is>
+      <c r="E12" t="n">
+        <v>3000000</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -9858,20 +9799,16 @@
           <t>잡급</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>100000</t>
-        </is>
+      <c r="C13" t="n">
+        <v>100000</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
           <t>현금</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>100000</t>
-        </is>
+      <c r="E13" t="n">
+        <v>100000</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -9888,20 +9825,16 @@
           <t>받을어음</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>2050000</t>
-        </is>
+      <c r="C14" t="n">
+        <v>2050000</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
           <t>상품매출</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2050000</t>
-        </is>
+      <c r="E14" t="n">
+        <v>2050000</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -9918,20 +9851,16 @@
           <t>차량운반구</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>20000000</t>
-        </is>
+      <c r="C15" t="n">
+        <v>20000000</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
           <t>자산수증이익</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>20000000</t>
-        </is>
+      <c r="E15" t="n">
+        <v>20000000</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -9948,20 +9877,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>200000</t>
-        </is>
+      <c r="C16" t="n">
+        <v>200000</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
           <t>선수금</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>200000</t>
-        </is>
+      <c r="E16" t="n">
+        <v>200000</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -9978,20 +9903,16 @@
           <t>단기매매증권</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>50010000</t>
-        </is>
+      <c r="C17" t="n">
+        <v>50010000</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
           <t>보통예금</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>50010000</t>
-        </is>
+      <c r="E17" t="n">
+        <v>50010000</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -10008,20 +9929,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>1000000</t>
-        </is>
+      <c r="C18" t="n">
+        <v>1000000</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>1000000</t>
-        </is>
+      <c r="E18" t="n">
+        <v>1000000</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -10038,20 +9955,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>26000000</t>
-        </is>
+      <c r="C19" t="n">
+        <v>26000000</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
           <t>단기차입금</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>26000000</t>
-        </is>
+      <c r="E19" t="n">
+        <v>26000000</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -10068,20 +9981,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>5000000</t>
-        </is>
+      <c r="C20" t="n">
+        <v>5000000</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
           <t>받을어음</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>5000000</t>
-        </is>
+      <c r="E20" t="n">
+        <v>5000000</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -10098,20 +10007,16 @@
           <t>비품</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>10000000</t>
-        </is>
+      <c r="C21" t="n">
+        <v>10000000</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
           <t>보통예금</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>10000000</t>
-        </is>
+      <c r="E21" t="n">
+        <v>10000000</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -10128,20 +10033,16 @@
           <t>기부금</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>5000000</t>
-        </is>
+      <c r="C22" t="n">
+        <v>5000000</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
           <t>보통예금</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>5000000</t>
-        </is>
+      <c r="E22" t="n">
+        <v>5000000</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -10158,20 +10059,16 @@
           <t>복리후생비(판)</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>180000</t>
-        </is>
+      <c r="C23" t="n">
+        <v>180000</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
           <t>보통예금</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>180000</t>
-        </is>
+      <c r="E23" t="n">
+        <v>180000</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -10188,20 +10085,16 @@
           <t>급여(판)</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>2100000</t>
-        </is>
+      <c r="C24" t="n">
+        <v>2100000</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
           <t>예수금</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2100000</t>
-        </is>
+      <c r="E24" t="n">
+        <v>2100000</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -10218,20 +10111,16 @@
           <t>세금과공과(판)</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>259740</t>
-        </is>
+      <c r="C25" t="n">
+        <v>259740</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
           <t>현금</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>259740</t>
-        </is>
+      <c r="E25" t="n">
+        <v>259740</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -10248,20 +10137,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>1000000</t>
-        </is>
+      <c r="C26" t="n">
+        <v>1000000</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>1000000</t>
-        </is>
+      <c r="E26" t="n">
+        <v>1000000</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -10278,20 +10163,16 @@
           <t>수선비(판)</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>2200000</t>
-        </is>
+      <c r="C27" t="n">
+        <v>2200000</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
           <t>보통예금</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>2200000</t>
-        </is>
+      <c r="E27" t="n">
+        <v>2200000</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -10308,20 +10189,16 @@
           <t>퇴직급여충당부채</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>3000000</t>
-        </is>
+      <c r="C28" t="n">
+        <v>3000000</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
           <t>보통예금</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>3000000</t>
-        </is>
+      <c r="E28" t="n">
+        <v>3000000</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -10338,20 +10215,16 @@
           <t>상</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>4500000</t>
-        </is>
+      <c r="C29" t="n">
+        <v>4500000</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
           <t>받을어음</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>4500000</t>
-        </is>
+      <c r="E29" t="n">
+        <v>4500000</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -10368,20 +10241,16 @@
           <t>선급금</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>500000</t>
-        </is>
+      <c r="C30" t="n">
+        <v>500000</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
           <t>보통예금</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>500000</t>
-        </is>
+      <c r="E30" t="n">
+        <v>500000</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -10398,20 +10267,16 @@
           <t>복리후생비(판)</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>100000</t>
-        </is>
+      <c r="C31" t="n">
+        <v>100000</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
           <t>현</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>100000</t>
-        </is>
+      <c r="E31" t="n">
+        <v>100000</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -10428,20 +10293,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>1000000</t>
-        </is>
+      <c r="C32" t="n">
+        <v>1000000</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>1000000</t>
-        </is>
+      <c r="E32" t="n">
+        <v>1000000</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -10458,20 +10319,16 @@
           <t>선수금</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>3062500</t>
-        </is>
+      <c r="C33" t="n">
+        <v>3062500</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
           <t>상품매출</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>3062500</t>
-        </is>
+      <c r="E33" t="n">
+        <v>3062500</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -10488,20 +10345,16 @@
           <t>교육훈련비</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>1000000</t>
-        </is>
+      <c r="C34" t="n">
+        <v>1000000</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
           <t>보통예금</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>1000000</t>
-        </is>
+      <c r="E34" t="n">
+        <v>1000000</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -10518,20 +10371,16 @@
           <t>비품</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>8000000</t>
-        </is>
+      <c r="C35" t="n">
+        <v>8000000</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
           <t>선급금</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>8000000</t>
-        </is>
+      <c r="E35" t="n">
+        <v>8000000</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -10548,20 +10397,16 @@
           <t>상품</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>7560000</t>
-        </is>
+      <c r="C36" t="n">
+        <v>7560000</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
           <t>현금</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>7560000</t>
-        </is>
+      <c r="E36" t="n">
+        <v>7560000</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -10578,20 +10423,16 @@
           <t>외상매입금</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>10000000</t>
-        </is>
+      <c r="C37" t="n">
+        <v>10000000</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
           <t>받을어음</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>10000000</t>
-        </is>
+      <c r="E37" t="n">
+        <v>10000000</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -10608,20 +10449,16 @@
           <t>급여(판)</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>2550000</t>
-        </is>
+      <c r="C38" t="n">
+        <v>2550000</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
           <t>예수금</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>2550000</t>
-        </is>
+      <c r="E38" t="n">
+        <v>2550000</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -10638,20 +10475,16 @@
           <t>차량유지비(판)</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>880000</t>
-        </is>
+      <c r="C39" t="n">
+        <v>880000</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
           <t>미지급금또는미지급비용</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>880000</t>
-        </is>
+      <c r="E39" t="n">
+        <v>880000</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -10668,20 +10501,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>1000000</t>
-        </is>
+      <c r="C40" t="n">
+        <v>1000000</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>1000000</t>
-        </is>
+      <c r="E40" t="n">
+        <v>1000000</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -10698,20 +10527,16 @@
           <t>예수금</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>920000</t>
-        </is>
+      <c r="C41" t="n">
+        <v>920000</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
           <t>보통예금</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>920000</t>
-        </is>
+      <c r="E41" t="n">
+        <v>920000</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -10728,20 +10553,16 @@
           <t>기부금</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>1000000</t>
-        </is>
+      <c r="C42" t="n">
+        <v>1000000</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
           <t>보통예금</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>1000000</t>
-        </is>
+      <c r="E42" t="n">
+        <v>1000000</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -10758,20 +10579,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>200000000</t>
-        </is>
+      <c r="C43" t="n">
+        <v>200000000</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
           <t>장기차입금</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>200000000</t>
-        </is>
+      <c r="E43" t="n">
+        <v>200000000</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -10788,20 +10605,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>15000000</t>
-        </is>
+      <c r="C44" t="n">
+        <v>15000000</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
           <t>상품매출</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>15000000</t>
-        </is>
+      <c r="E44" t="n">
+        <v>15000000</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -10818,20 +10631,16 @@
           <t>수선비(판)</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>120000</t>
-        </is>
+      <c r="C45" t="n">
+        <v>120000</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
           <t>미지급금또는미지급비용</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>120000</t>
-        </is>
+      <c r="E45" t="n">
+        <v>120000</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -10848,20 +10657,16 @@
           <t>수수료비용(판)</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>700000</t>
-        </is>
+      <c r="C46" t="n">
+        <v>700000</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
           <t>예수금</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>700000</t>
-        </is>
+      <c r="E46" t="n">
+        <v>700000</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -10878,20 +10683,16 @@
           <t>기업업무추진비</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>500000</t>
-        </is>
+      <c r="C47" t="n">
+        <v>500000</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
           <t>미지급금또는미지급비용</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>500000</t>
-        </is>
+      <c r="E47" t="n">
+        <v>500000</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -10908,20 +10709,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>1000000</t>
-        </is>
+      <c r="C48" t="n">
+        <v>1000000</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>1000000</t>
-        </is>
+      <c r="E48" t="n">
+        <v>1000000</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -10938,20 +10735,16 @@
           <t>인출금</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>11000000</t>
-        </is>
+      <c r="C49" t="n">
+        <v>11000000</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
           <t>현금</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>11000000</t>
-        </is>
+      <c r="E49" t="n">
+        <v>11000000</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -10968,20 +10761,16 @@
           <t>운반비(판)</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>30000</t>
-        </is>
+      <c r="C50" t="n">
+        <v>30000</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
           <t>현</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>30000</t>
-        </is>
+      <c r="E50" t="n">
+        <v>30000</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -10998,20 +10787,16 @@
           <t>여비교통비(판)</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>420000</t>
-        </is>
+      <c r="C51" t="n">
+        <v>420000</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
           <t>가지급금</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>420000</t>
-        </is>
+      <c r="E51" t="n">
+        <v>420000</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -11028,20 +10813,16 @@
           <t>외상매입금</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>5001000</t>
-        </is>
+      <c r="C52" t="n">
+        <v>5001000</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
           <t>보통예금</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>5001000</t>
-        </is>
+      <c r="E52" t="n">
+        <v>5001000</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -11058,20 +10839,16 @@
           <t>대손충당금</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>200000</t>
-        </is>
+      <c r="C53" t="n">
+        <v>200000</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>200000</t>
-        </is>
+      <c r="E53" t="n">
+        <v>200000</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -11088,20 +10865,16 @@
           <t>장기차입금</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>1000000</t>
-        </is>
+      <c r="C54" t="n">
+        <v>1000000</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
           <t>보통예금</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>1000000</t>
-        </is>
+      <c r="E54" t="n">
+        <v>1000000</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -11118,20 +10891,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>1000000</t>
-        </is>
+      <c r="C55" t="n">
+        <v>1000000</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>1000000</t>
-        </is>
+      <c r="E55" t="n">
+        <v>1000000</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -11148,20 +10917,16 @@
           <t>복리후생비(판)</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>4300000</t>
-        </is>
+      <c r="C56" t="n">
+        <v>4300000</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
           <t>현</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>4300000</t>
-        </is>
+      <c r="E56" t="n">
+        <v>4300000</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -11178,20 +10943,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>300000</t>
-        </is>
+      <c r="C57" t="n">
+        <v>300000</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
           <t>선수금</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>300000</t>
-        </is>
+      <c r="E57" t="n">
+        <v>300000</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -11208,20 +10969,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>50000000</t>
-        </is>
+      <c r="C58" t="n">
+        <v>50000000</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
           <t>장기차입금</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>50000000</t>
-        </is>
+      <c r="E58" t="n">
+        <v>50000000</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -11238,20 +10995,16 @@
           <t>급여(판)</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>2717000</t>
-        </is>
+      <c r="C59" t="n">
+        <v>2717000</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
           <t>예수금</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>2717000</t>
-        </is>
+      <c r="E59" t="n">
+        <v>2717000</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -11268,20 +11021,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>2000000</t>
-        </is>
+      <c r="C60" t="n">
+        <v>2000000</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
           <t>받을어음</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>2000000</t>
-        </is>
+      <c r="E60" t="n">
+        <v>2000000</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -11298,20 +11047,16 @@
           <t>상</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>4150000</t>
-        </is>
+      <c r="C61" t="n">
+        <v>4150000</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
           <t>외상매입금</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>4150000</t>
-        </is>
+      <c r="E61" t="n">
+        <v>4150000</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -11328,20 +11073,16 @@
           <t>교육훈련비</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>1000000</t>
-        </is>
+      <c r="C62" t="n">
+        <v>1000000</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
           <t>보통예금</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>1000000</t>
-        </is>
+      <c r="E62" t="n">
+        <v>1000000</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -11358,20 +11099,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>1000000</t>
-        </is>
+      <c r="C63" t="n">
+        <v>1000000</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>1000000</t>
-        </is>
+      <c r="E63" t="n">
+        <v>1000000</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -11388,20 +11125,16 @@
           <t>수선비(판)</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>1050000</t>
-        </is>
+      <c r="C64" t="n">
+        <v>1050000</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
           <t>미지급금또는미지급비용</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>1050000</t>
-        </is>
+      <c r="E64" t="n">
+        <v>1050000</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -11418,20 +11151,16 @@
           <t>외상매입금</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>3000000</t>
-        </is>
+      <c r="C65" t="n">
+        <v>3000000</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
           <t>현금</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>3000000</t>
-        </is>
+      <c r="E65" t="n">
+        <v>3000000</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -11448,20 +11177,16 @@
           <t>기부금</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>500000</t>
-        </is>
+      <c r="C66" t="n">
+        <v>500000</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
           <t>현금</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>500000</t>
-        </is>
+      <c r="E66" t="n">
+        <v>500000</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -11478,20 +11203,16 @@
           <t>임차보증금</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>10000000</t>
-        </is>
+      <c r="C67" t="n">
+        <v>10000000</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
           <t>보통예금</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>10000000</t>
-        </is>
+      <c r="E67" t="n">
+        <v>10000000</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -11508,20 +11229,16 @@
           <t>감가상각누계액</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>20000000</t>
-        </is>
+      <c r="C68" t="n">
+        <v>20000000</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
           <t>기계장치</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>20000000</t>
-        </is>
+      <c r="E68" t="n">
+        <v>20000000</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -11538,20 +11255,16 @@
           <t>차량운반구</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>32100000</t>
-        </is>
+      <c r="C69" t="n">
+        <v>32100000</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
           <t>보통예금</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>32100000</t>
-        </is>
+      <c r="E69" t="n">
+        <v>32100000</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -11568,20 +11281,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>1000000</t>
-        </is>
+      <c r="C70" t="n">
+        <v>1000000</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>1000000</t>
-        </is>
+      <c r="E70" t="n">
+        <v>1000000</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -11598,20 +11307,16 @@
           <t>단기차입금</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>8050000</t>
-        </is>
+      <c r="C71" t="n">
+        <v>8050000</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
           <t>당좌예금</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>8050000</t>
-        </is>
+      <c r="E71" t="n">
+        <v>8050000</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -11628,20 +11333,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>5000000</t>
-        </is>
+      <c r="C72" t="n">
+        <v>5000000</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>5000000</t>
-        </is>
+      <c r="E72" t="n">
+        <v>5000000</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -11658,20 +11359,16 @@
           <t>토</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>1000000</t>
-        </is>
+      <c r="C73" t="n">
+        <v>1000000</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
           <t>현</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>1000000</t>
-        </is>
+      <c r="E73" t="n">
+        <v>1000000</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -11688,20 +11385,16 @@
           <t>임차료(판)</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>800000</t>
-        </is>
+      <c r="C74" t="n">
+        <v>800000</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
           <t>보통예금</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>800000</t>
-        </is>
+      <c r="E74" t="n">
+        <v>800000</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -11718,20 +11411,16 @@
           <t>잡급</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>100000</t>
-        </is>
+      <c r="C75" t="n">
+        <v>100000</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
           <t>현금</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>100000</t>
-        </is>
+      <c r="E75" t="n">
+        <v>100000</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -11748,20 +11437,16 @@
           <t>선급금</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>4500000</t>
-        </is>
+      <c r="C76" t="n">
+        <v>4500000</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
           <t>당좌예금</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>4500000</t>
-        </is>
+      <c r="E76" t="n">
+        <v>4500000</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -11778,20 +11463,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>1000000</t>
-        </is>
+      <c r="C77" t="n">
+        <v>1000000</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>1000000</t>
-        </is>
+      <c r="E77" t="n">
+        <v>1000000</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -11808,20 +11489,16 @@
           <t>현</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>2600000</t>
-        </is>
+      <c r="C78" t="n">
+        <v>2600000</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>2600000</t>
-        </is>
+      <c r="E78" t="n">
+        <v>2600000</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -11838,20 +11515,16 @@
           <t>예수금</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>220000</t>
-        </is>
+      <c r="C79" t="n">
+        <v>220000</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
           <t>보통예금</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>220000</t>
-        </is>
+      <c r="E79" t="n">
+        <v>220000</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -11868,20 +11541,16 @@
           <t>세금과공과(판)</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>500000</t>
-        </is>
+      <c r="C80" t="n">
+        <v>500000</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
           <t>현</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>500000</t>
-        </is>
+      <c r="E80" t="n">
+        <v>500000</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -11898,20 +11567,16 @@
           <t>지급어음</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>3500000</t>
-        </is>
+      <c r="C81" t="n">
+        <v>3500000</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
           <t>보통예금</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>3500000</t>
-        </is>
+      <c r="E81" t="n">
+        <v>3500000</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -11928,20 +11593,16 @@
           <t>현</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>10000000</t>
-        </is>
+      <c r="C82" t="n">
+        <v>10000000</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
           <t>상품매출</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>10000000</t>
-        </is>
+      <c r="E82" t="n">
+        <v>10000000</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -11958,20 +11619,16 @@
           <t>수도광열비(판)</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>130000</t>
-        </is>
+      <c r="C83" t="n">
+        <v>130000</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
           <t>미지급금또는미지급비용</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>130000</t>
-        </is>
+      <c r="E83" t="n">
+        <v>130000</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -11988,20 +11645,16 @@
           <t>선납세금</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>100000</t>
-        </is>
+      <c r="C84" t="n">
+        <v>100000</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
           <t>이자수익</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>100000</t>
-        </is>
+      <c r="E84" t="n">
+        <v>100000</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -12018,20 +11671,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>300000</t>
-        </is>
+      <c r="C85" t="n">
+        <v>300000</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>300000</t>
-        </is>
+      <c r="E85" t="n">
+        <v>300000</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -12048,20 +11697,16 @@
           <t>선급금</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>7500000</t>
-        </is>
+      <c r="C86" t="n">
+        <v>7500000</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
           <t>현</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>7500000</t>
-        </is>
+      <c r="E86" t="n">
+        <v>7500000</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -12078,20 +11723,16 @@
           <t>급여(판)</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>3700000</t>
-        </is>
+      <c r="C87" t="n">
+        <v>3700000</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>3700000</t>
-        </is>
+      <c r="E87" t="n">
+        <v>3700000</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -12108,20 +11749,16 @@
           <t>기업업무추진비</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>3000000</t>
-        </is>
+      <c r="C88" t="n">
+        <v>3000000</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
           <t>미지급금또는미지급비용</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>3000000</t>
-        </is>
+      <c r="E88" t="n">
+        <v>3000000</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -12138,20 +11775,16 @@
           <t>당좌예금</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>35000000</t>
-        </is>
+      <c r="C89" t="n">
+        <v>35000000</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
           <t>상품매출</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>35000000</t>
-        </is>
+      <c r="E89" t="n">
+        <v>35000000</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -12168,20 +11801,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>4000000</t>
-        </is>
+      <c r="C90" t="n">
+        <v>4000000</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>4000000</t>
-        </is>
+      <c r="E90" t="n">
+        <v>4000000</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -12198,20 +11827,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>4000000</t>
-        </is>
+      <c r="C91" t="n">
+        <v>4000000</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
           <t>대손충당금</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>4000000</t>
-        </is>
+      <c r="E91" t="n">
+        <v>4000000</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -12228,20 +11853,16 @@
           <t>임차보증금</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>20000000</t>
-        </is>
+      <c r="C92" t="n">
+        <v>20000000</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
           <t>보통예금</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>20000000</t>
-        </is>
+      <c r="E92" t="n">
+        <v>20000000</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -12258,20 +11879,16 @@
           <t>인출금</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>1500000</t>
-        </is>
+      <c r="C93" t="n">
+        <v>1500000</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
           <t>미지급금</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>1500000</t>
-        </is>
+      <c r="E93" t="n">
+        <v>1500000</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -12288,20 +11905,16 @@
           <t>현</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>11000000</t>
-        </is>
+      <c r="C94" t="n">
+        <v>11000000</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
           <t>차량운반구</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>11000000</t>
-        </is>
+      <c r="E94" t="n">
+        <v>11000000</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -12318,20 +11931,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>10000000</t>
-        </is>
+      <c r="C95" t="n">
+        <v>10000000</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
           <t>장기차입금</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>10000000</t>
-        </is>
+      <c r="E95" t="n">
+        <v>10000000</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -12348,20 +11957,16 @@
           <t>상</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>2200000</t>
-        </is>
+      <c r="C96" t="n">
+        <v>2200000</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
           <t>외상매입금</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>2200000</t>
-        </is>
+      <c r="E96" t="n">
+        <v>2200000</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -12378,20 +11983,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>1000000</t>
-        </is>
+      <c r="C97" t="n">
+        <v>1000000</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>1000000</t>
-        </is>
+      <c r="E97" t="n">
+        <v>1000000</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12408,20 +12009,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>15600000</t>
-        </is>
+      <c r="C98" t="n">
+        <v>15600000</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
           <t>선수금</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>15600000</t>
-        </is>
+      <c r="E98" t="n">
+        <v>15600000</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12438,20 +12035,16 @@
           <t>세금과공과(판)</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>120000</t>
-        </is>
+      <c r="C99" t="n">
+        <v>120000</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
           <t>현</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>120000</t>
-        </is>
+      <c r="E99" t="n">
+        <v>120000</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12468,20 +12061,16 @@
           <t>당좌예금</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>1800000</t>
-        </is>
+      <c r="C100" t="n">
+        <v>1800000</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>1800000</t>
-        </is>
+      <c r="E100" t="n">
+        <v>1800000</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12498,20 +12087,16 @@
           <t>복리후생비(판)</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>200000</t>
-        </is>
+      <c r="C101" t="n">
+        <v>200000</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
           <t>현</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>200000</t>
-        </is>
+      <c r="E101" t="n">
+        <v>200000</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12528,20 +12113,16 @@
           <t>광고선전비(판)</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>500000</t>
-        </is>
+      <c r="C102" t="n">
+        <v>500000</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
           <t>미지급금또는미지급비용</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>500000</t>
-        </is>
+      <c r="E102" t="n">
+        <v>500000</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12558,20 +12139,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>1000000</t>
-        </is>
+      <c r="C103" t="n">
+        <v>1000000</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>1000000</t>
-        </is>
+      <c r="E103" t="n">
+        <v>1000000</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12588,20 +12165,16 @@
           <t>단기매매증권</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>11612000</t>
-        </is>
+      <c r="C104" t="n">
+        <v>11612000</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
           <t>보통예금</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>11612000</t>
-        </is>
+      <c r="E104" t="n">
+        <v>11612000</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12618,20 +12191,16 @@
           <t>비품</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>550000</t>
-        </is>
+      <c r="C105" t="n">
+        <v>550000</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
           <t>현금</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>550000</t>
-        </is>
+      <c r="E105" t="n">
+        <v>550000</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12648,20 +12217,16 @@
           <t>예수금</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>440000</t>
-        </is>
+      <c r="C106" t="n">
+        <v>440000</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
           <t>보통예금</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>440000</t>
-        </is>
+      <c r="E106" t="n">
+        <v>440000</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12678,20 +12243,16 @@
           <t>광고선전비(판)</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>990000</t>
-        </is>
+      <c r="C107" t="n">
+        <v>990000</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
           <t>당좌예금</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>990000</t>
-        </is>
+      <c r="E107" t="n">
+        <v>990000</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12708,20 +12269,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>10500000</t>
-        </is>
+      <c r="C108" t="n">
+        <v>10500000</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
           <t>정기예금</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>10500000</t>
-        </is>
+      <c r="E108" t="n">
+        <v>10500000</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12738,20 +12295,16 @@
           <t>수선비(판)</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>330000</t>
-        </is>
+      <c r="C109" t="n">
+        <v>330000</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
           <t>미지급금또는미지급비용</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>330000</t>
-        </is>
+      <c r="E109" t="n">
+        <v>330000</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12768,20 +12321,16 @@
           <t>선급금</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>1000000</t>
-        </is>
+      <c r="C110" t="n">
+        <v>1000000</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
           <t>보통예금</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>1000000</t>
-        </is>
+      <c r="E110" t="n">
+        <v>1000000</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12798,20 +12347,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>2000000</t>
-        </is>
+      <c r="C111" t="n">
+        <v>2000000</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>2000000</t>
-        </is>
+      <c r="E111" t="n">
+        <v>2000000</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12828,20 +12373,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>15000000</t>
-        </is>
+      <c r="C112" t="n">
+        <v>15000000</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>15000000</t>
-        </is>
+      <c r="E112" t="n">
+        <v>15000000</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12858,20 +12399,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>2000000</t>
-        </is>
+      <c r="C113" t="n">
+        <v>2000000</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>2000000</t>
-        </is>
+      <c r="E113" t="n">
+        <v>2000000</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12888,20 +12425,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>1000000</t>
-        </is>
+      <c r="C114" t="n">
+        <v>1000000</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>1000000</t>
-        </is>
+      <c r="E114" t="n">
+        <v>1000000</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12918,20 +12451,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>3000000</t>
-        </is>
+      <c r="C115" t="n">
+        <v>3000000</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>3000000</t>
-        </is>
+      <c r="E115" t="n">
+        <v>3000000</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12948,20 +12477,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>8286160</t>
-        </is>
+      <c r="C116" t="n">
+        <v>8286160</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>8286160</t>
-        </is>
+      <c r="E116" t="n">
+        <v>8286160</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12978,20 +12503,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>25000</t>
-        </is>
+      <c r="C117" t="n">
+        <v>25000</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>25000</t>
-        </is>
+      <c r="E117" t="n">
+        <v>25000</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13008,20 +12529,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>400000</t>
-        </is>
+      <c r="C118" t="n">
+        <v>400000</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>400000</t>
-        </is>
+      <c r="E118" t="n">
+        <v>400000</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13038,20 +12555,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>300000</t>
-        </is>
+      <c r="C119" t="n">
+        <v>300000</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>300000</t>
-        </is>
+      <c r="E119" t="n">
+        <v>300000</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13068,20 +12581,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>5000000</t>
-        </is>
+      <c r="C120" t="n">
+        <v>5000000</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>5000000</t>
-        </is>
+      <c r="E120" t="n">
+        <v>5000000</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13098,20 +12607,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>250000</t>
-        </is>
+      <c r="C121" t="n">
+        <v>250000</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>250000</t>
-        </is>
+      <c r="E121" t="n">
+        <v>250000</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13128,20 +12633,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>3500</t>
-        </is>
+      <c r="C122" t="n">
+        <v>3500</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>3500</t>
-        </is>
+      <c r="E122" t="n">
+        <v>3500</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13158,20 +12659,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>60000</t>
-        </is>
+      <c r="C123" t="n">
+        <v>60000</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>60000</t>
-        </is>
+      <c r="E123" t="n">
+        <v>60000</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13188,20 +12685,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>3000000</t>
-        </is>
+      <c r="C124" t="n">
+        <v>3000000</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>3000000</t>
-        </is>
+      <c r="E124" t="n">
+        <v>3000000</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13218,20 +12711,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>3000000</t>
-        </is>
+      <c r="C125" t="n">
+        <v>3000000</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>3000000</t>
-        </is>
+      <c r="E125" t="n">
+        <v>3000000</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13248,20 +12737,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>2500000</t>
-        </is>
+      <c r="C126" t="n">
+        <v>2500000</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>2500000</t>
-        </is>
+      <c r="E126" t="n">
+        <v>2500000</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13278,20 +12763,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>3000000</t>
-        </is>
+      <c r="C127" t="n">
+        <v>3000000</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>3000000</t>
-        </is>
+      <c r="E127" t="n">
+        <v>3000000</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13308,20 +12789,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>5000000</t>
-        </is>
+      <c r="C128" t="n">
+        <v>5000000</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>5000000</t>
-        </is>
+      <c r="E128" t="n">
+        <v>5000000</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13338,20 +12815,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>2000000</t>
-        </is>
+      <c r="C129" t="n">
+        <v>2000000</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>2000000</t>
-        </is>
+      <c r="E129" t="n">
+        <v>2000000</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13368,20 +12841,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>5000000</t>
-        </is>
+      <c r="C130" t="n">
+        <v>5000000</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>5000000</t>
-        </is>
+      <c r="E130" t="n">
+        <v>5000000</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13398,20 +12867,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>50000</t>
-        </is>
+      <c r="C131" t="n">
+        <v>50000</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>50000</t>
-        </is>
+      <c r="E131" t="n">
+        <v>50000</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13428,20 +12893,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>3000000</t>
-        </is>
+      <c r="C132" t="n">
+        <v>3000000</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>3000000</t>
-        </is>
+      <c r="E132" t="n">
+        <v>3000000</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13458,20 +12919,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>300000</t>
-        </is>
+      <c r="C133" t="n">
+        <v>300000</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>300000</t>
-        </is>
+      <c r="E133" t="n">
+        <v>300000</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13488,20 +12945,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>50000</t>
-        </is>
+      <c r="C134" t="n">
+        <v>50000</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>50000</t>
-        </is>
+      <c r="E134" t="n">
+        <v>50000</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13518,20 +12971,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>22000000</t>
-        </is>
+      <c r="C135" t="n">
+        <v>22000000</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>22000000</t>
-        </is>
+      <c r="E135" t="n">
+        <v>22000000</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13548,20 +12997,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>1000000</t>
-        </is>
+      <c r="C136" t="n">
+        <v>1000000</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>1000000</t>
-        </is>
+      <c r="E136" t="n">
+        <v>1000000</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13578,20 +13023,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>100000</t>
-        </is>
+      <c r="C137" t="n">
+        <v>100000</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>100000</t>
-        </is>
+      <c r="E137" t="n">
+        <v>100000</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13608,20 +13049,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>330000</t>
-        </is>
+      <c r="C138" t="n">
+        <v>330000</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>330000</t>
-        </is>
+      <c r="E138" t="n">
+        <v>330000</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13638,20 +13075,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>6000000</t>
-        </is>
+      <c r="C139" t="n">
+        <v>6000000</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>6000000</t>
-        </is>
+      <c r="E139" t="n">
+        <v>6000000</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13668,20 +13101,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>6000000</t>
-        </is>
+      <c r="C140" t="n">
+        <v>6000000</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>6000000</t>
-        </is>
+      <c r="E140" t="n">
+        <v>6000000</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13698,20 +13127,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>20000000</t>
-        </is>
+      <c r="C141" t="n">
+        <v>20000000</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>20000000</t>
-        </is>
+      <c r="E141" t="n">
+        <v>20000000</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13728,20 +13153,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>2000000</t>
-        </is>
+      <c r="C142" t="n">
+        <v>2000000</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>2000000</t>
-        </is>
+      <c r="E142" t="n">
+        <v>2000000</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13758,20 +13179,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>500000</t>
-        </is>
+      <c r="C143" t="n">
+        <v>500000</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>500000</t>
-        </is>
+      <c r="E143" t="n">
+        <v>500000</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13788,20 +13205,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>28000</t>
-        </is>
+      <c r="C144" t="n">
+        <v>28000</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>28000</t>
-        </is>
+      <c r="E144" t="n">
+        <v>28000</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13818,20 +13231,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>700000</t>
-        </is>
+      <c r="C145" t="n">
+        <v>700000</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>700000</t>
-        </is>
+      <c r="E145" t="n">
+        <v>700000</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13848,20 +13257,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>120000</t>
-        </is>
+      <c r="C146" t="n">
+        <v>120000</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>120000</t>
-        </is>
+      <c r="E146" t="n">
+        <v>120000</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13878,20 +13283,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>100000</t>
-        </is>
+      <c r="C147" t="n">
+        <v>100000</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>100000</t>
-        </is>
+      <c r="E147" t="n">
+        <v>100000</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13908,20 +13309,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>1200000</t>
-        </is>
+      <c r="C148" t="n">
+        <v>1200000</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>1200000</t>
-        </is>
+      <c r="E148" t="n">
+        <v>1200000</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13938,20 +13335,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>12000000</t>
-        </is>
+      <c r="C149" t="n">
+        <v>12000000</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>12000000</t>
-        </is>
+      <c r="E149" t="n">
+        <v>12000000</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13968,20 +13361,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>30800</t>
-        </is>
+      <c r="C150" t="n">
+        <v>30800</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>30800</t>
-        </is>
+      <c r="E150" t="n">
+        <v>30800</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13998,20 +13387,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>500000</t>
-        </is>
+      <c r="C151" t="n">
+        <v>500000</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>500000</t>
-        </is>
+      <c r="E151" t="n">
+        <v>500000</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14028,20 +13413,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>5000000</t>
-        </is>
+      <c r="C152" t="n">
+        <v>5000000</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>5000000</t>
-        </is>
+      <c r="E152" t="n">
+        <v>5000000</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14058,20 +13439,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>300000</t>
-        </is>
+      <c r="C153" t="n">
+        <v>300000</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>300000</t>
-        </is>
+      <c r="E153" t="n">
+        <v>300000</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14088,20 +13465,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>200000</t>
-        </is>
+      <c r="C154" t="n">
+        <v>200000</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>200000</t>
-        </is>
+      <c r="E154" t="n">
+        <v>200000</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14118,20 +13491,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>4000000</t>
-        </is>
+      <c r="C155" t="n">
+        <v>4000000</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>4000000</t>
-        </is>
+      <c r="E155" t="n">
+        <v>4000000</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14148,20 +13517,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>900000</t>
-        </is>
+      <c r="C156" t="n">
+        <v>900000</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>900000</t>
-        </is>
+      <c r="E156" t="n">
+        <v>900000</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14178,20 +13543,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>10000000</t>
-        </is>
+      <c r="C157" t="n">
+        <v>10000000</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>10000000</t>
-        </is>
+      <c r="E157" t="n">
+        <v>10000000</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14208,20 +13569,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>1500000</t>
-        </is>
+      <c r="C158" t="n">
+        <v>1500000</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>1500000</t>
-        </is>
+      <c r="E158" t="n">
+        <v>1500000</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14238,20 +13595,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>30000</t>
-        </is>
+      <c r="C159" t="n">
+        <v>30000</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>30000</t>
-        </is>
+      <c r="E159" t="n">
+        <v>30000</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14268,20 +13621,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>500000</t>
-        </is>
+      <c r="C160" t="n">
+        <v>500000</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>500000</t>
-        </is>
+      <c r="E160" t="n">
+        <v>500000</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14298,20 +13647,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>20000</t>
-        </is>
+      <c r="C161" t="n">
+        <v>20000</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>20000</t>
-        </is>
+      <c r="E161" t="n">
+        <v>20000</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14328,20 +13673,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>300000</t>
-        </is>
+      <c r="C162" t="n">
+        <v>300000</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>300000</t>
-        </is>
+      <c r="E162" t="n">
+        <v>300000</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14358,20 +13699,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>200000</t>
-        </is>
+      <c r="C163" t="n">
+        <v>200000</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>200000</t>
-        </is>
+      <c r="E163" t="n">
+        <v>200000</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14388,20 +13725,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>1500000</t>
-        </is>
+      <c r="C164" t="n">
+        <v>1500000</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>1500000</t>
-        </is>
+      <c r="E164" t="n">
+        <v>1500000</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14418,20 +13751,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>2000000</t>
-        </is>
+      <c r="C165" t="n">
+        <v>2000000</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>2000000</t>
-        </is>
+      <c r="E165" t="n">
+        <v>2000000</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14448,20 +13777,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>5000000</t>
-        </is>
+      <c r="C166" t="n">
+        <v>5000000</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>5000000</t>
-        </is>
+      <c r="E166" t="n">
+        <v>5000000</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14478,20 +13803,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>2000000</t>
-        </is>
+      <c r="C167" t="n">
+        <v>2000000</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>2000000</t>
-        </is>
+      <c r="E167" t="n">
+        <v>2000000</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14508,20 +13829,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>10000000</t>
-        </is>
+      <c r="C168" t="n">
+        <v>10000000</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>10000000</t>
-        </is>
+      <c r="E168" t="n">
+        <v>10000000</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14538,20 +13855,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>100000</t>
-        </is>
+      <c r="C169" t="n">
+        <v>100000</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>100000</t>
-        </is>
+      <c r="E169" t="n">
+        <v>100000</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14568,20 +13881,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>20000</t>
-        </is>
+      <c r="C170" t="n">
+        <v>20000</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>20000</t>
-        </is>
+      <c r="E170" t="n">
+        <v>20000</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14598,20 +13907,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>142789500</t>
-        </is>
+      <c r="C171" t="n">
+        <v>142789500</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>142789500</t>
-        </is>
+      <c r="E171" t="n">
+        <v>142789500</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14628,20 +13933,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>2000000</t>
-        </is>
+      <c r="C172" t="n">
+        <v>2000000</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>2000000</t>
-        </is>
+      <c r="E172" t="n">
+        <v>2000000</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14658,20 +13959,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>200000</t>
-        </is>
+      <c r="C173" t="n">
+        <v>200000</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>200000</t>
-        </is>
+      <c r="E173" t="n">
+        <v>200000</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14688,20 +13985,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>500000</t>
-        </is>
+      <c r="C174" t="n">
+        <v>500000</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>500000</t>
-        </is>
+      <c r="E174" t="n">
+        <v>500000</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14718,20 +14011,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>15000000</t>
-        </is>
+      <c r="C175" t="n">
+        <v>15000000</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>15000000</t>
-        </is>
+      <c r="E175" t="n">
+        <v>15000000</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14748,20 +14037,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>12000000</t>
-        </is>
+      <c r="C176" t="n">
+        <v>12000000</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>12000000</t>
-        </is>
+      <c r="E176" t="n">
+        <v>12000000</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14778,20 +14063,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>300000</t>
-        </is>
+      <c r="C177" t="n">
+        <v>300000</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>300000</t>
-        </is>
+      <c r="E177" t="n">
+        <v>300000</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14808,20 +14089,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>3000000</t>
-        </is>
+      <c r="C178" t="n">
+        <v>3000000</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>3000000</t>
-        </is>
+      <c r="E178" t="n">
+        <v>3000000</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14838,20 +14115,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>500000</t>
-        </is>
+      <c r="C179" t="n">
+        <v>500000</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>500000</t>
-        </is>
+      <c r="E179" t="n">
+        <v>500000</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14868,20 +14141,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>1550000</t>
-        </is>
+      <c r="C180" t="n">
+        <v>1550000</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>1550000</t>
-        </is>
+      <c r="E180" t="n">
+        <v>1550000</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14898,20 +14167,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>22000000</t>
-        </is>
+      <c r="C181" t="n">
+        <v>22000000</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>22000000</t>
-        </is>
+      <c r="E181" t="n">
+        <v>22000000</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14928,20 +14193,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>60000</t>
-        </is>
+      <c r="C182" t="n">
+        <v>60000</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>60000</t>
-        </is>
+      <c r="E182" t="n">
+        <v>60000</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14958,20 +14219,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>330000</t>
-        </is>
+      <c r="C183" t="n">
+        <v>330000</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>330000</t>
-        </is>
+      <c r="E183" t="n">
+        <v>330000</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14988,20 +14245,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>2000000</t>
-        </is>
+      <c r="C184" t="n">
+        <v>2000000</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>2000000</t>
-        </is>
+      <c r="E184" t="n">
+        <v>2000000</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15018,20 +14271,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>200000</t>
-        </is>
+      <c r="C185" t="n">
+        <v>200000</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>200000</t>
-        </is>
+      <c r="E185" t="n">
+        <v>200000</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15048,20 +14297,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>7000000</t>
-        </is>
+      <c r="C186" t="n">
+        <v>7000000</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>7000000</t>
-        </is>
+      <c r="E186" t="n">
+        <v>7000000</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15078,20 +14323,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>5000000</t>
-        </is>
+      <c r="C187" t="n">
+        <v>5000000</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>5000000</t>
-        </is>
+      <c r="E187" t="n">
+        <v>5000000</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15108,20 +14349,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>1100000</t>
-        </is>
+      <c r="C188" t="n">
+        <v>1100000</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>1100000</t>
-        </is>
+      <c r="E188" t="n">
+        <v>1100000</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15138,20 +14375,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>6000000</t>
-        </is>
+      <c r="C189" t="n">
+        <v>6000000</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>6000000</t>
-        </is>
+      <c r="E189" t="n">
+        <v>6000000</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15168,20 +14401,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>7800000</t>
-        </is>
+      <c r="C190" t="n">
+        <v>7800000</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>7800000</t>
-        </is>
+      <c r="E190" t="n">
+        <v>7800000</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15198,20 +14427,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>600000</t>
-        </is>
+      <c r="C191" t="n">
+        <v>600000</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t>600000</t>
-        </is>
+      <c r="E191" t="n">
+        <v>600000</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15228,20 +14453,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>270000</t>
-        </is>
+      <c r="C192" t="n">
+        <v>270000</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E192" t="inlineStr">
-        <is>
-          <t>270000</t>
-        </is>
+      <c r="E192" t="n">
+        <v>270000</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15258,20 +14479,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>1000000</t>
-        </is>
+      <c r="C193" t="n">
+        <v>1000000</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E193" t="inlineStr">
-        <is>
-          <t>1000000</t>
-        </is>
+      <c r="E193" t="n">
+        <v>1000000</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15288,20 +14505,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>300000</t>
-        </is>
+      <c r="C194" t="n">
+        <v>300000</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E194" t="inlineStr">
-        <is>
-          <t>300000</t>
-        </is>
+      <c r="E194" t="n">
+        <v>300000</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15318,20 +14531,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>5000000</t>
-        </is>
+      <c r="C195" t="n">
+        <v>5000000</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E195" t="inlineStr">
-        <is>
-          <t>5000000</t>
-        </is>
+      <c r="E195" t="n">
+        <v>5000000</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15348,20 +14557,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>3000000</t>
-        </is>
+      <c r="C196" t="n">
+        <v>3000000</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E196" t="inlineStr">
-        <is>
-          <t>3000000</t>
-        </is>
+      <c r="E196" t="n">
+        <v>3000000</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15378,20 +14583,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>300000</t>
-        </is>
+      <c r="C197" t="n">
+        <v>300000</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E197" t="inlineStr">
-        <is>
-          <t>300000</t>
-        </is>
+      <c r="E197" t="n">
+        <v>300000</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15408,20 +14609,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>2700000</t>
-        </is>
+      <c r="C198" t="n">
+        <v>2700000</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E198" t="inlineStr">
-        <is>
-          <t>2700000</t>
-        </is>
+      <c r="E198" t="n">
+        <v>2700000</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15438,20 +14635,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
+      <c r="C199" t="n">
+        <v>1000</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E199" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
+      <c r="E199" t="n">
+        <v>1000</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15468,20 +14661,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>3000000</t>
-        </is>
+      <c r="C200" t="n">
+        <v>3000000</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E200" t="inlineStr">
-        <is>
-          <t>3000000</t>
-        </is>
+      <c r="E200" t="n">
+        <v>3000000</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15498,20 +14687,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>2000000</t>
-        </is>
+      <c r="C201" t="n">
+        <v>2000000</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E201" t="inlineStr">
-        <is>
-          <t>2000000</t>
-        </is>
+      <c r="E201" t="n">
+        <v>2000000</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15528,20 +14713,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>1500000</t>
-        </is>
+      <c r="C202" t="n">
+        <v>1500000</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E202" t="inlineStr">
-        <is>
-          <t>1500000</t>
-        </is>
+      <c r="E202" t="n">
+        <v>1500000</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15558,20 +14739,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>2500000</t>
-        </is>
+      <c r="C203" t="n">
+        <v>2500000</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E203" t="inlineStr">
-        <is>
-          <t>2500000</t>
-        </is>
+      <c r="E203" t="n">
+        <v>2500000</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -15588,20 +14765,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>1200000</t>
-        </is>
+      <c r="C204" t="n">
+        <v>1200000</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E204" t="inlineStr">
-        <is>
-          <t>1200000</t>
-        </is>
+      <c r="E204" t="n">
+        <v>1200000</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -15618,20 +14791,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C205" t="inlineStr">
-        <is>
-          <t>5000000</t>
-        </is>
+      <c r="C205" t="n">
+        <v>5000000</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E205" t="inlineStr">
-        <is>
-          <t>5000000</t>
-        </is>
+      <c r="E205" t="n">
+        <v>5000000</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -15648,20 +14817,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>400000</t>
-        </is>
+      <c r="C206" t="n">
+        <v>400000</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E206" t="inlineStr">
-        <is>
-          <t>400000</t>
-        </is>
+      <c r="E206" t="n">
+        <v>400000</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -15678,20 +14843,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>90000</t>
-        </is>
+      <c r="C207" t="n">
+        <v>90000</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E207" t="inlineStr">
-        <is>
-          <t>90000</t>
-        </is>
+      <c r="E207" t="n">
+        <v>90000</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -15708,20 +14869,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>310000</t>
-        </is>
+      <c r="C208" t="n">
+        <v>310000</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E208" t="inlineStr">
-        <is>
-          <t>310000</t>
-        </is>
+      <c r="E208" t="n">
+        <v>310000</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -15738,20 +14895,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>10000000</t>
-        </is>
+      <c r="C209" t="n">
+        <v>10000000</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E209" t="inlineStr">
-        <is>
-          <t>10000000</t>
-        </is>
+      <c r="E209" t="n">
+        <v>10000000</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -15768,20 +14921,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>315000</t>
-        </is>
+      <c r="C210" t="n">
+        <v>315000</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E210" t="inlineStr">
-        <is>
-          <t>315000</t>
-        </is>
+      <c r="E210" t="n">
+        <v>315000</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -15798,20 +14947,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>20000000</t>
-        </is>
+      <c r="C211" t="n">
+        <v>20000000</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E211" t="inlineStr">
-        <is>
-          <t>20000000</t>
-        </is>
+      <c r="E211" t="n">
+        <v>20000000</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -15828,20 +14973,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>200000</t>
-        </is>
+      <c r="C212" t="n">
+        <v>200000</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E212" t="inlineStr">
-        <is>
-          <t>200000</t>
-        </is>
+      <c r="E212" t="n">
+        <v>200000</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -15858,20 +14999,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>2000000</t>
-        </is>
+      <c r="C213" t="n">
+        <v>2000000</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E213" t="inlineStr">
-        <is>
-          <t>2000000</t>
-        </is>
+      <c r="E213" t="n">
+        <v>2000000</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -15888,20 +15025,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>2000000</t>
-        </is>
+      <c r="C214" t="n">
+        <v>2000000</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E214" t="inlineStr">
-        <is>
-          <t>2000000</t>
-        </is>
+      <c r="E214" t="n">
+        <v>2000000</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -15918,20 +15051,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>1000000</t>
-        </is>
+      <c r="C215" t="n">
+        <v>1000000</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E215" t="inlineStr">
-        <is>
-          <t>1000000</t>
-        </is>
+      <c r="E215" t="n">
+        <v>1000000</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -15948,20 +15077,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>15000000</t>
-        </is>
+      <c r="C216" t="n">
+        <v>15000000</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E216" t="inlineStr">
-        <is>
-          <t>15000000</t>
-        </is>
+      <c r="E216" t="n">
+        <v>15000000</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -15978,20 +15103,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>30000000</t>
-        </is>
+      <c r="C217" t="n">
+        <v>30000000</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E217" t="inlineStr">
-        <is>
-          <t>30000000</t>
-        </is>
+      <c r="E217" t="n">
+        <v>30000000</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -16008,20 +15129,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>30000</t>
-        </is>
+      <c r="C218" t="n">
+        <v>30000</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E218" t="inlineStr">
-        <is>
-          <t>30000</t>
-        </is>
+      <c r="E218" t="n">
+        <v>30000</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -16038,20 +15155,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>20000000</t>
-        </is>
+      <c r="C219" t="n">
+        <v>20000000</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E219" t="inlineStr">
-        <is>
-          <t>20000000</t>
-        </is>
+      <c r="E219" t="n">
+        <v>20000000</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -16068,20 +15181,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>5000000</t>
-        </is>
+      <c r="C220" t="n">
+        <v>5000000</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E220" t="inlineStr">
-        <is>
-          <t>5000000</t>
-        </is>
+      <c r="E220" t="n">
+        <v>5000000</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -16098,20 +15207,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>1000000</t>
-        </is>
+      <c r="C221" t="n">
+        <v>1000000</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E221" t="inlineStr">
-        <is>
-          <t>1000000</t>
-        </is>
+      <c r="E221" t="n">
+        <v>1000000</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -16128,20 +15233,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C222" t="inlineStr">
-        <is>
-          <t>500000</t>
-        </is>
+      <c r="C222" t="n">
+        <v>500000</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E222" t="inlineStr">
-        <is>
-          <t>500000</t>
-        </is>
+      <c r="E222" t="n">
+        <v>500000</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -16158,20 +15259,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C223" t="inlineStr">
-        <is>
-          <t>500000</t>
-        </is>
+      <c r="C223" t="n">
+        <v>500000</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E223" t="inlineStr">
-        <is>
-          <t>500000</t>
-        </is>
+      <c r="E223" t="n">
+        <v>500000</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -16188,20 +15285,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C224" t="inlineStr">
-        <is>
-          <t>300000</t>
-        </is>
+      <c r="C224" t="n">
+        <v>300000</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E224" t="inlineStr">
-        <is>
-          <t>300000</t>
-        </is>
+      <c r="E224" t="n">
+        <v>300000</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -16218,20 +15311,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C225" t="inlineStr">
-        <is>
-          <t>9000000</t>
-        </is>
+      <c r="C225" t="n">
+        <v>9000000</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E225" t="inlineStr">
-        <is>
-          <t>9000000</t>
-        </is>
+      <c r="E225" t="n">
+        <v>9000000</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -16248,20 +15337,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C226" t="inlineStr">
-        <is>
-          <t>120000</t>
-        </is>
+      <c r="C226" t="n">
+        <v>120000</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E226" t="inlineStr">
-        <is>
-          <t>120000</t>
-        </is>
+      <c r="E226" t="n">
+        <v>120000</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -16278,20 +15363,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C227" t="inlineStr">
-        <is>
-          <t>550000</t>
-        </is>
+      <c r="C227" t="n">
+        <v>550000</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E227" t="inlineStr">
-        <is>
-          <t>550000</t>
-        </is>
+      <c r="E227" t="n">
+        <v>550000</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -16308,20 +15389,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C228" t="inlineStr">
-        <is>
-          <t>30000000</t>
-        </is>
+      <c r="C228" t="n">
+        <v>30000000</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E228" t="inlineStr">
-        <is>
-          <t>30000000</t>
-        </is>
+      <c r="E228" t="n">
+        <v>30000000</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -16338,20 +15415,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C229" t="inlineStr">
-        <is>
-          <t>2000000</t>
-        </is>
+      <c r="C229" t="n">
+        <v>2000000</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E229" t="inlineStr">
-        <is>
-          <t>2000000</t>
-        </is>
+      <c r="E229" t="n">
+        <v>2000000</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -16368,20 +15441,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C230" t="inlineStr">
-        <is>
-          <t>200000</t>
-        </is>
+      <c r="C230" t="n">
+        <v>200000</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E230" t="inlineStr">
-        <is>
-          <t>200000</t>
-        </is>
+      <c r="E230" t="n">
+        <v>200000</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -16398,20 +15467,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C231" t="inlineStr">
-        <is>
-          <t>1000000</t>
-        </is>
+      <c r="C231" t="n">
+        <v>1000000</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E231" t="inlineStr">
-        <is>
-          <t>1000000</t>
-        </is>
+      <c r="E231" t="n">
+        <v>1000000</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -16428,20 +15493,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C232" t="inlineStr">
-        <is>
-          <t>4500000</t>
-        </is>
+      <c r="C232" t="n">
+        <v>4500000</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E232" t="inlineStr">
-        <is>
-          <t>4500000</t>
-        </is>
+      <c r="E232" t="n">
+        <v>4500000</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -16458,20 +15519,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C233" t="inlineStr">
-        <is>
-          <t>30000</t>
-        </is>
+      <c r="C233" t="n">
+        <v>30000</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E233" t="inlineStr">
-        <is>
-          <t>30000</t>
-        </is>
+      <c r="E233" t="n">
+        <v>30000</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -16488,20 +15545,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C234" t="inlineStr">
-        <is>
-          <t>30000</t>
-        </is>
+      <c r="C234" t="n">
+        <v>30000</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E234" t="inlineStr">
-        <is>
-          <t>30000</t>
-        </is>
+      <c r="E234" t="n">
+        <v>30000</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -16518,20 +15571,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C235" t="inlineStr">
-        <is>
-          <t>77000</t>
-        </is>
+      <c r="C235" t="n">
+        <v>77000</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E235" t="inlineStr">
-        <is>
-          <t>77000</t>
-        </is>
+      <c r="E235" t="n">
+        <v>77000</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -16548,20 +15597,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C236" t="inlineStr">
-        <is>
-          <t>2000000</t>
-        </is>
+      <c r="C236" t="n">
+        <v>2000000</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E236" t="inlineStr">
-        <is>
-          <t>2000000</t>
-        </is>
+      <c r="E236" t="n">
+        <v>2000000</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -16578,20 +15623,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C237" t="inlineStr">
-        <is>
-          <t>22000</t>
-        </is>
+      <c r="C237" t="n">
+        <v>22000</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E237" t="inlineStr">
-        <is>
-          <t>22000</t>
-        </is>
+      <c r="E237" t="n">
+        <v>22000</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -16608,20 +15649,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C238" t="inlineStr">
-        <is>
-          <t>52000</t>
-        </is>
+      <c r="C238" t="n">
+        <v>52000</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E238" t="inlineStr">
-        <is>
-          <t>52000</t>
-        </is>
+      <c r="E238" t="n">
+        <v>52000</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -16638,20 +15675,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C239" t="inlineStr">
-        <is>
-          <t>500000</t>
-        </is>
+      <c r="C239" t="n">
+        <v>500000</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E239" t="inlineStr">
-        <is>
-          <t>500000</t>
-        </is>
+      <c r="E239" t="n">
+        <v>500000</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -16668,20 +15701,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C240" t="inlineStr">
-        <is>
-          <t>120000</t>
-        </is>
+      <c r="C240" t="n">
+        <v>120000</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E240" t="inlineStr">
-        <is>
-          <t>120000</t>
-        </is>
+      <c r="E240" t="n">
+        <v>120000</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -16698,20 +15727,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C241" t="inlineStr">
-        <is>
-          <t>500000</t>
-        </is>
+      <c r="C241" t="n">
+        <v>500000</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E241" t="inlineStr">
-        <is>
-          <t>500000</t>
-        </is>
+      <c r="E241" t="n">
+        <v>500000</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -16728,20 +15753,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C242" t="inlineStr">
-        <is>
-          <t>20000</t>
-        </is>
+      <c r="C242" t="n">
+        <v>20000</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E242" t="inlineStr">
-        <is>
-          <t>20000</t>
-        </is>
+      <c r="E242" t="n">
+        <v>20000</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -16758,20 +15779,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C243" t="inlineStr">
-        <is>
-          <t>300000</t>
-        </is>
+      <c r="C243" t="n">
+        <v>300000</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E243" t="inlineStr">
-        <is>
-          <t>300000</t>
-        </is>
+      <c r="E243" t="n">
+        <v>300000</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -16788,20 +15805,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C244" t="inlineStr">
-        <is>
-          <t>130000</t>
-        </is>
+      <c r="C244" t="n">
+        <v>130000</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E244" t="inlineStr">
-        <is>
-          <t>130000</t>
-        </is>
+      <c r="E244" t="n">
+        <v>130000</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -16818,20 +15831,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C245" t="inlineStr">
-        <is>
-          <t>400000</t>
-        </is>
+      <c r="C245" t="n">
+        <v>400000</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E245" t="inlineStr">
-        <is>
-          <t>400000</t>
-        </is>
+      <c r="E245" t="n">
+        <v>400000</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -16848,20 +15857,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C246" t="inlineStr">
-        <is>
-          <t>51000</t>
-        </is>
+      <c r="C246" t="n">
+        <v>51000</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E246" t="inlineStr">
-        <is>
-          <t>51000</t>
-        </is>
+      <c r="E246" t="n">
+        <v>51000</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -16878,20 +15883,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C247" t="inlineStr">
-        <is>
-          <t>100000</t>
-        </is>
+      <c r="C247" t="n">
+        <v>100000</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E247" t="inlineStr">
-        <is>
-          <t>100000</t>
-        </is>
+      <c r="E247" t="n">
+        <v>100000</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -16908,20 +15909,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C248" t="inlineStr">
-        <is>
-          <t>200000</t>
-        </is>
+      <c r="C248" t="n">
+        <v>200000</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E248" t="inlineStr">
-        <is>
-          <t>200000</t>
-        </is>
+      <c r="E248" t="n">
+        <v>200000</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -16938,20 +15935,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C249" t="inlineStr">
-        <is>
-          <t>88000</t>
-        </is>
+      <c r="C249" t="n">
+        <v>88000</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E249" t="inlineStr">
-        <is>
-          <t>88000</t>
-        </is>
+      <c r="E249" t="n">
+        <v>88000</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -16968,20 +15961,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C250" t="inlineStr">
-        <is>
-          <t>33000</t>
-        </is>
+      <c r="C250" t="n">
+        <v>33000</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E250" t="inlineStr">
-        <is>
-          <t>33000</t>
-        </is>
+      <c r="E250" t="n">
+        <v>33000</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -16998,20 +15987,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C251" t="inlineStr">
-        <is>
-          <t>12500</t>
-        </is>
+      <c r="C251" t="n">
+        <v>12500</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E251" t="inlineStr">
-        <is>
-          <t>12500</t>
-        </is>
+      <c r="E251" t="n">
+        <v>12500</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -17028,20 +16013,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C252" t="inlineStr">
-        <is>
-          <t>178000</t>
-        </is>
+      <c r="C252" t="n">
+        <v>178000</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E252" t="inlineStr">
-        <is>
-          <t>178000</t>
-        </is>
+      <c r="E252" t="n">
+        <v>178000</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -17058,20 +16039,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C253" t="inlineStr">
-        <is>
-          <t>78500</t>
-        </is>
+      <c r="C253" t="n">
+        <v>78500</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E253" t="inlineStr">
-        <is>
-          <t>78500</t>
-        </is>
+      <c r="E253" t="n">
+        <v>78500</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -17088,20 +16065,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C254" t="inlineStr">
-        <is>
-          <t>750000</t>
-        </is>
+      <c r="C254" t="n">
+        <v>750000</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E254" t="inlineStr">
-        <is>
-          <t>750000</t>
-        </is>
+      <c r="E254" t="n">
+        <v>750000</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -17118,20 +16091,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C255" t="inlineStr">
-        <is>
-          <t>61000</t>
-        </is>
+      <c r="C255" t="n">
+        <v>61000</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E255" t="inlineStr">
-        <is>
-          <t>61000</t>
-        </is>
+      <c r="E255" t="n">
+        <v>61000</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -17148,20 +16117,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C256" t="inlineStr">
-        <is>
-          <t>5000000</t>
-        </is>
+      <c r="C256" t="n">
+        <v>5000000</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E256" t="inlineStr">
-        <is>
-          <t>5000000</t>
-        </is>
+      <c r="E256" t="n">
+        <v>5000000</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -17178,20 +16143,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C257" t="inlineStr">
-        <is>
-          <t>300000</t>
-        </is>
+      <c r="C257" t="n">
+        <v>300000</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E257" t="inlineStr">
-        <is>
-          <t>300000</t>
-        </is>
+      <c r="E257" t="n">
+        <v>300000</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -17208,20 +16169,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C258" t="inlineStr">
-        <is>
-          <t>500000</t>
-        </is>
+      <c r="C258" t="n">
+        <v>500000</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E258" t="inlineStr">
-        <is>
-          <t>500000</t>
-        </is>
+      <c r="E258" t="n">
+        <v>500000</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -17238,20 +16195,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C259" t="inlineStr">
-        <is>
-          <t>89700</t>
-        </is>
+      <c r="C259" t="n">
+        <v>89700</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E259" t="inlineStr">
-        <is>
-          <t>89700</t>
-        </is>
+      <c r="E259" t="n">
+        <v>89700</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -17268,20 +16221,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C260" t="inlineStr">
-        <is>
-          <t>112000</t>
-        </is>
+      <c r="C260" t="n">
+        <v>112000</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E260" t="inlineStr">
-        <is>
-          <t>112000</t>
-        </is>
+      <c r="E260" t="n">
+        <v>112000</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -17298,20 +16247,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C261" t="inlineStr">
-        <is>
-          <t>340000</t>
-        </is>
+      <c r="C261" t="n">
+        <v>340000</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E261" t="inlineStr">
-        <is>
-          <t>340000</t>
-        </is>
+      <c r="E261" t="n">
+        <v>340000</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -17328,20 +16273,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C262" t="inlineStr">
-        <is>
-          <t>55000</t>
-        </is>
+      <c r="C262" t="n">
+        <v>55000</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E262" t="inlineStr">
-        <is>
-          <t>55000</t>
-        </is>
+      <c r="E262" t="n">
+        <v>55000</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -17358,20 +16299,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C263" t="inlineStr">
-        <is>
-          <t>276000</t>
-        </is>
+      <c r="C263" t="n">
+        <v>276000</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E263" t="inlineStr">
-        <is>
-          <t>276000</t>
-        </is>
+      <c r="E263" t="n">
+        <v>276000</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -17388,20 +16325,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C264" t="inlineStr">
-        <is>
-          <t>228500</t>
-        </is>
+      <c r="C264" t="n">
+        <v>228500</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E264" t="inlineStr">
-        <is>
-          <t>228500</t>
-        </is>
+      <c r="E264" t="n">
+        <v>228500</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -17418,20 +16351,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C265" t="inlineStr">
-        <is>
-          <t>89000</t>
-        </is>
+      <c r="C265" t="n">
+        <v>89000</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E265" t="inlineStr">
-        <is>
-          <t>89000</t>
-        </is>
+      <c r="E265" t="n">
+        <v>89000</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -17448,20 +16377,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C266" t="inlineStr">
-        <is>
-          <t>280000</t>
-        </is>
+      <c r="C266" t="n">
+        <v>280000</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E266" t="inlineStr">
-        <is>
-          <t>280000</t>
-        </is>
+      <c r="E266" t="n">
+        <v>280000</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -17478,20 +16403,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C267" t="inlineStr">
-        <is>
-          <t>33000</t>
-        </is>
+      <c r="C267" t="n">
+        <v>33000</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E267" t="inlineStr">
-        <is>
-          <t>33000</t>
-        </is>
+      <c r="E267" t="n">
+        <v>33000</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -17508,20 +16429,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C268" t="inlineStr">
-        <is>
-          <t>34000</t>
-        </is>
+      <c r="C268" t="n">
+        <v>34000</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E268" t="inlineStr">
-        <is>
-          <t>34000</t>
-        </is>
+      <c r="E268" t="n">
+        <v>34000</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -17538,20 +16455,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C269" t="inlineStr">
-        <is>
-          <t>110000</t>
-        </is>
+      <c r="C269" t="n">
+        <v>110000</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E269" t="inlineStr">
-        <is>
-          <t>110000</t>
-        </is>
+      <c r="E269" t="n">
+        <v>110000</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -17568,20 +16481,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C270" t="inlineStr">
-        <is>
-          <t>2000000</t>
-        </is>
+      <c r="C270" t="n">
+        <v>2000000</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E270" t="inlineStr">
-        <is>
-          <t>2000000</t>
-        </is>
+      <c r="E270" t="n">
+        <v>2000000</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -17598,20 +16507,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C271" t="inlineStr">
-        <is>
-          <t>390000</t>
-        </is>
+      <c r="C271" t="n">
+        <v>390000</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E271" t="inlineStr">
-        <is>
-          <t>390000</t>
-        </is>
+      <c r="E271" t="n">
+        <v>390000</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -17628,20 +16533,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C272" t="inlineStr">
-        <is>
-          <t>760000</t>
-        </is>
+      <c r="C272" t="n">
+        <v>760000</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E272" t="inlineStr">
-        <is>
-          <t>760000</t>
-        </is>
+      <c r="E272" t="n">
+        <v>760000</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -17658,20 +16559,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C273" t="inlineStr">
-        <is>
-          <t>89000</t>
-        </is>
+      <c r="C273" t="n">
+        <v>89000</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E273" t="inlineStr">
-        <is>
-          <t>89000</t>
-        </is>
+      <c r="E273" t="n">
+        <v>89000</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -17688,20 +16585,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C274" t="inlineStr">
-        <is>
-          <t>10000</t>
-        </is>
+      <c r="C274" t="n">
+        <v>10000</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E274" t="inlineStr">
-        <is>
-          <t>10000</t>
-        </is>
+      <c r="E274" t="n">
+        <v>10000</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -17718,20 +16611,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C275" t="inlineStr">
-        <is>
-          <t>300000</t>
-        </is>
+      <c r="C275" t="n">
+        <v>300000</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E275" t="inlineStr">
-        <is>
-          <t>300000</t>
-        </is>
+      <c r="E275" t="n">
+        <v>300000</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -17748,20 +16637,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C276" t="inlineStr">
-        <is>
-          <t>450000</t>
-        </is>
+      <c r="C276" t="n">
+        <v>450000</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E276" t="inlineStr">
-        <is>
-          <t>450000</t>
-        </is>
+      <c r="E276" t="n">
+        <v>450000</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -17778,20 +16663,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C277" t="inlineStr">
-        <is>
-          <t>150000</t>
-        </is>
+      <c r="C277" t="n">
+        <v>150000</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E277" t="inlineStr">
-        <is>
-          <t>150000</t>
-        </is>
+      <c r="E277" t="n">
+        <v>150000</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -17808,20 +16689,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C278" t="inlineStr">
-        <is>
-          <t>200000</t>
-        </is>
+      <c r="C278" t="n">
+        <v>200000</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E278" t="inlineStr">
-        <is>
-          <t>200000</t>
-        </is>
+      <c r="E278" t="n">
+        <v>200000</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -17838,20 +16715,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C279" t="inlineStr">
-        <is>
-          <t>500000</t>
-        </is>
+      <c r="C279" t="n">
+        <v>500000</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E279" t="inlineStr">
-        <is>
-          <t>500000</t>
-        </is>
+      <c r="E279" t="n">
+        <v>500000</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -17868,20 +16741,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C280" t="inlineStr">
-        <is>
-          <t>10000000</t>
-        </is>
+      <c r="C280" t="n">
+        <v>10000000</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E280" t="inlineStr">
-        <is>
-          <t>10000000</t>
-        </is>
+      <c r="E280" t="n">
+        <v>10000000</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -17898,20 +16767,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C281" t="inlineStr">
-        <is>
-          <t>110000</t>
-        </is>
+      <c r="C281" t="n">
+        <v>110000</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E281" t="inlineStr">
-        <is>
-          <t>110000</t>
-        </is>
+      <c r="E281" t="n">
+        <v>110000</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -17928,20 +16793,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C282" t="inlineStr">
-        <is>
-          <t>13000000</t>
-        </is>
+      <c r="C282" t="n">
+        <v>13000000</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E282" t="inlineStr">
-        <is>
-          <t>13000000</t>
-        </is>
+      <c r="E282" t="n">
+        <v>13000000</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -17958,20 +16819,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C283" t="inlineStr">
-        <is>
-          <t>1100</t>
-        </is>
+      <c r="C283" t="n">
+        <v>1100</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E283" t="inlineStr">
-        <is>
-          <t>1100</t>
-        </is>
+      <c r="E283" t="n">
+        <v>1100</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -17988,20 +16845,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C284" t="inlineStr">
-        <is>
-          <t>12000000</t>
-        </is>
+      <c r="C284" t="n">
+        <v>12000000</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E284" t="inlineStr">
-        <is>
-          <t>12000000</t>
-        </is>
+      <c r="E284" t="n">
+        <v>12000000</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -18018,20 +16871,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C285" t="inlineStr">
-        <is>
-          <t>1100</t>
-        </is>
+      <c r="C285" t="n">
+        <v>1100</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E285" t="inlineStr">
-        <is>
-          <t>1100</t>
-        </is>
+      <c r="E285" t="n">
+        <v>1100</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -18048,20 +16897,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C286" t="inlineStr">
-        <is>
-          <t>2000000</t>
-        </is>
+      <c r="C286" t="n">
+        <v>2000000</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E286" t="inlineStr">
-        <is>
-          <t>2000000</t>
-        </is>
+      <c r="E286" t="n">
+        <v>2000000</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -18078,20 +16923,16 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C287" t="inlineStr">
-        <is>
-          <t>1000000</t>
-        </is>
+      <c r="C287" t="n">
+        <v>1000000</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
           <t>외상매출금</t>
         </is>
       </c>
-      <c r="E287" t="inlineStr">
-        <is>
-          <t>1000000</t>
-        </is>
+      <c r="E287" t="n">
+        <v>1000000</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
